--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/43.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/43.xlsx
@@ -426,13 +426,13 @@
         <v>-23.80073658272469</v>
       </c>
       <c r="E2">
-        <v>-22.02971123016394</v>
+        <v>-19.26861480930468</v>
       </c>
       <c r="F2">
-        <v>-1.593112194474503</v>
+        <v>0.248749471771753</v>
       </c>
       <c r="G2">
-        <v>-16.26113701434203</v>
+        <v>-18.45112225880084</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-23.59599535334129</v>
       </c>
       <c r="E3">
-        <v>-21.19408926481976</v>
+        <v>-19.78303156399794</v>
       </c>
       <c r="F3">
-        <v>-2.169575555184887</v>
+        <v>0.3878870309503747</v>
       </c>
       <c r="G3">
-        <v>-15.83851359604949</v>
+        <v>-17.82211295371932</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-23.01121263950894</v>
       </c>
       <c r="E4">
-        <v>-22.54217597553453</v>
+        <v>-20.20499783460052</v>
       </c>
       <c r="F4">
-        <v>-1.429309995877526</v>
+        <v>0.3567023117045846</v>
       </c>
       <c r="G4">
-        <v>-15.88409328049345</v>
+        <v>-17.4833309872258</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.03642963197126</v>
       </c>
       <c r="E5">
-        <v>-23.67931692984994</v>
+        <v>-20.37183233351888</v>
       </c>
       <c r="F5">
-        <v>-1.944391332040467</v>
+        <v>0.5345776441077223</v>
       </c>
       <c r="G5">
-        <v>-15.54259091813599</v>
+        <v>-17.25492738592766</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.72177309854468</v>
       </c>
       <c r="E6">
-        <v>-22.91005082184254</v>
+        <v>-21.01160131241812</v>
       </c>
       <c r="F6">
-        <v>-1.553956095711573</v>
+        <v>0.2005981313818233</v>
       </c>
       <c r="G6">
-        <v>-15.84536810597346</v>
+        <v>-16.96874147996671</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.11731174952767</v>
       </c>
       <c r="E7">
-        <v>-23.41807993751822</v>
+        <v>-21.74883785468843</v>
       </c>
       <c r="F7">
-        <v>-2.355579656911697</v>
+        <v>0.4487977144456252</v>
       </c>
       <c r="G7">
-        <v>-15.13815916815433</v>
+        <v>-16.0772100578981</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.30858892912182</v>
       </c>
       <c r="E8">
-        <v>-24.1306214852511</v>
+        <v>-21.87304379256875</v>
       </c>
       <c r="F8">
-        <v>-1.606177205151457</v>
+        <v>0.2436765497970088</v>
       </c>
       <c r="G8">
-        <v>-14.20995853293123</v>
+        <v>-16.2624384705207</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.36017424424684</v>
       </c>
       <c r="E9">
-        <v>-24.57589973101995</v>
+        <v>-22.47596548059412</v>
       </c>
       <c r="F9">
-        <v>-1.539423217996859</v>
+        <v>0.5157571367161177</v>
       </c>
       <c r="G9">
-        <v>-14.60069431678791</v>
+        <v>-14.99535404976502</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.36374026382793</v>
       </c>
       <c r="E10">
-        <v>-25.28231529204871</v>
+        <v>-22.8468472519013</v>
       </c>
       <c r="F10">
-        <v>-1.068370437660114</v>
+        <v>0.9536122650182691</v>
       </c>
       <c r="G10">
-        <v>-13.85637103386151</v>
+        <v>-14.73229150864756</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.37149361074809</v>
       </c>
       <c r="E11">
-        <v>-26.16270887547454</v>
+        <v>-25.24202498898655</v>
       </c>
       <c r="F11">
-        <v>-1.582554651925823</v>
+        <v>0.5564473719090322</v>
       </c>
       <c r="G11">
-        <v>-14.1411353893926</v>
+        <v>-14.28280744462936</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.464111935726324</v>
       </c>
       <c r="E12">
-        <v>-25.63614813086748</v>
+        <v>-24.27954733693681</v>
       </c>
       <c r="F12">
-        <v>-1.553803676109458</v>
+        <v>0.8540971754503534</v>
       </c>
       <c r="G12">
-        <v>-13.03330899943943</v>
+        <v>-13.41476619701929</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.677381490086784</v>
       </c>
       <c r="E13">
-        <v>-26.87708198940167</v>
+        <v>-24.77144122661553</v>
       </c>
       <c r="F13">
-        <v>-1.953017121805818</v>
+        <v>0.8395377899787492</v>
       </c>
       <c r="G13">
-        <v>-12.68412582649492</v>
+        <v>-13.51004532087197</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.076241406762999</v>
       </c>
       <c r="E14">
-        <v>-27.34308891289273</v>
+        <v>-25.38313865017025</v>
       </c>
       <c r="F14">
-        <v>-0.7706957830967089</v>
+        <v>0.9406996739434305</v>
       </c>
       <c r="G14">
-        <v>-12.18392674342204</v>
+        <v>-11.95704129010364</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.679176638505095</v>
       </c>
       <c r="E15">
-        <v>-26.84113594538528</v>
+        <v>-25.93814889235238</v>
       </c>
       <c r="F15">
-        <v>-1.485122078008545</v>
+        <v>1.043632607415297</v>
       </c>
       <c r="G15">
-        <v>-11.65710067626441</v>
+        <v>-11.47425065196431</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.515165838254049</v>
       </c>
       <c r="E16">
-        <v>-28.47550766593181</v>
+        <v>-26.73708554206435</v>
       </c>
       <c r="F16">
-        <v>-1.42463303352132</v>
+        <v>1.283385328072752</v>
       </c>
       <c r="G16">
-        <v>-11.4372668440866</v>
+        <v>-11.20568205050419</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.571892360704934</v>
       </c>
       <c r="E17">
-        <v>-28.95153213513836</v>
+        <v>-26.82288258161266</v>
       </c>
       <c r="F17">
-        <v>-1.222107972313077</v>
+        <v>1.13973813675329</v>
       </c>
       <c r="G17">
-        <v>-10.06177125418495</v>
+        <v>-10.93062052724597</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.83707693678241</v>
       </c>
       <c r="E18">
-        <v>-29.3861968493666</v>
+        <v>-28.25485170145499</v>
       </c>
       <c r="F18">
-        <v>-0.6358955556391455</v>
+        <v>1.345849200448252</v>
       </c>
       <c r="G18">
-        <v>-10.4389403037739</v>
+        <v>-10.0998293834619</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.276656546613421</v>
       </c>
       <c r="E19">
-        <v>-30.85428644810097</v>
+        <v>-28.34443231652022</v>
       </c>
       <c r="F19">
-        <v>-0.3589706761484651</v>
+        <v>1.652192719881954</v>
       </c>
       <c r="G19">
-        <v>-9.212120091474677</v>
+        <v>-10.02111282329525</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.8594828413551892</v>
       </c>
       <c r="E20">
-        <v>-29.78970001902465</v>
+        <v>-28.97819367523809</v>
       </c>
       <c r="F20">
-        <v>-0.4265919639737943</v>
+        <v>1.13528483359584</v>
       </c>
       <c r="G20">
-        <v>-9.535315912759252</v>
+        <v>-9.830493223091997</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.5524982352825971</v>
       </c>
       <c r="E21">
-        <v>-30.72089568337579</v>
+        <v>-29.55060171965994</v>
       </c>
       <c r="F21">
-        <v>-0.5720218019440811</v>
+        <v>1.556738287322561</v>
       </c>
       <c r="G21">
-        <v>-9.050103809011665</v>
+        <v>-9.37985912608141</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.3276316818626835</v>
       </c>
       <c r="E22">
-        <v>-30.67239448152444</v>
+        <v>-30.80099036377511</v>
       </c>
       <c r="F22">
-        <v>-0.2604860756296319</v>
+        <v>1.949164090520382</v>
       </c>
       <c r="G22">
-        <v>-8.28745962591713</v>
+        <v>-8.936287093189785</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.1662608706557063</v>
       </c>
       <c r="E23">
-        <v>-31.59567620169611</v>
+        <v>-30.57146313990846</v>
       </c>
       <c r="F23">
-        <v>0.0640914670744928</v>
+        <v>1.459156607272779</v>
       </c>
       <c r="G23">
-        <v>-9.304789776108539</v>
+        <v>-8.965757178134272</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.0547769272548916</v>
       </c>
       <c r="E24">
-        <v>-31.88521317599521</v>
+        <v>-31.12443830854143</v>
       </c>
       <c r="F24">
-        <v>0.1956345539042487</v>
+        <v>2.06201589527337</v>
       </c>
       <c r="G24">
-        <v>-8.53989643654876</v>
+        <v>-8.816177177531028</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.008535651682993578</v>
       </c>
       <c r="E25">
-        <v>-34.42192197200229</v>
+        <v>-30.69630659572714</v>
       </c>
       <c r="F25">
-        <v>-0.3880778499480341</v>
+        <v>1.658857764004878</v>
       </c>
       <c r="G25">
-        <v>-9.938857398835337</v>
+        <v>-8.938279091312804</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.02400165243104185</v>
       </c>
       <c r="E26">
-        <v>-32.7311330288193</v>
+        <v>-30.58066250299295</v>
       </c>
       <c r="F26">
-        <v>-0.674499133344408</v>
+        <v>1.689691255471882</v>
       </c>
       <c r="G26">
-        <v>-8.741803590991688</v>
+        <v>-8.719045730390953</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.01353911325765982</v>
       </c>
       <c r="E27">
-        <v>-33.01710447119603</v>
+        <v>-30.73580571203192</v>
       </c>
       <c r="F27">
-        <v>-0.02839492508066921</v>
+        <v>2.28623838386314</v>
       </c>
       <c r="G27">
-        <v>-9.349261199473563</v>
+        <v>-9.020548874867966</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.1049524767374532</v>
       </c>
       <c r="E28">
-        <v>-32.82440792535796</v>
+        <v>-30.83352246808249</v>
       </c>
       <c r="F28">
-        <v>-0.4364777005588036</v>
+        <v>1.806439700487638</v>
       </c>
       <c r="G28">
-        <v>-9.38001185463999</v>
+        <v>-9.199508889727305</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.2487526886069525</v>
       </c>
       <c r="E29">
-        <v>-33.54964791671651</v>
+        <v>-30.63063186504763</v>
       </c>
       <c r="F29">
-        <v>-0.4764555397853106</v>
+        <v>1.802962214130686</v>
       </c>
       <c r="G29">
-        <v>-9.31038590713959</v>
+        <v>-9.267354309416566</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.4388373013590493</v>
       </c>
       <c r="E30">
-        <v>-31.88961557999952</v>
+        <v>-30.78702103748405</v>
       </c>
       <c r="F30">
-        <v>0.2301783029683909</v>
+        <v>1.845785495385809</v>
       </c>
       <c r="G30">
-        <v>-9.612070498365686</v>
+        <v>-8.907655057259046</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.6657459605447325</v>
       </c>
       <c r="E31">
-        <v>-32.69670498354213</v>
+        <v>-30.67293647560233</v>
       </c>
       <c r="F31">
-        <v>-0.5392217662628319</v>
+        <v>1.863327003507492</v>
       </c>
       <c r="G31">
-        <v>-9.86478535329627</v>
+        <v>-9.680333637189525</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.9197998447090665</v>
       </c>
       <c r="E32">
-        <v>-31.76385426447806</v>
+        <v>-30.82485886925889</v>
       </c>
       <c r="F32">
-        <v>-0.06087603931184062</v>
+        <v>2.009933123189754</v>
       </c>
       <c r="G32">
-        <v>-10.52755941817465</v>
+        <v>-10.00793770071619</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.187274121245813</v>
       </c>
       <c r="E33">
-        <v>-32.74397268163001</v>
+        <v>-30.08467562355361</v>
       </c>
       <c r="F33">
-        <v>-0.5685940176312968</v>
+        <v>2.292358362235023</v>
       </c>
       <c r="G33">
-        <v>-9.86044629578584</v>
+        <v>-9.523049329297905</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.458603254350151</v>
       </c>
       <c r="E34">
-        <v>-30.89524957139775</v>
+        <v>-29.95877725205843</v>
       </c>
       <c r="F34">
-        <v>-0.09947547518008919</v>
+        <v>1.979749071766546</v>
       </c>
       <c r="G34">
-        <v>-10.22919177795157</v>
+        <v>-9.320112236113783</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.721417108368613</v>
       </c>
       <c r="E35">
-        <v>-31.56158456653625</v>
+        <v>-29.31212017217696</v>
       </c>
       <c r="F35">
-        <v>0.2164522551040031</v>
+        <v>2.211075639202724</v>
       </c>
       <c r="G35">
-        <v>-10.15592514711886</v>
+        <v>-9.587304975174385</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.969915892704182</v>
       </c>
       <c r="E36">
-        <v>-30.10907158687566</v>
+        <v>-28.5992733634117</v>
       </c>
       <c r="F36">
-        <v>-0.1820438244215327</v>
+        <v>2.162404084083836</v>
       </c>
       <c r="G36">
-        <v>-9.539571426442766</v>
+        <v>-9.821252492611752</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.196284231286933</v>
       </c>
       <c r="E37">
-        <v>-30.91118959646244</v>
+        <v>-28.23060110052932</v>
       </c>
       <c r="F37">
-        <v>0.1156092925893997</v>
+        <v>2.432930653755293</v>
       </c>
       <c r="G37">
-        <v>-10.92928643675991</v>
+        <v>-9.637723674717964</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.398725448031587</v>
       </c>
       <c r="E38">
-        <v>-28.84718270060204</v>
+        <v>-28.3029791142871</v>
       </c>
       <c r="F38">
-        <v>-0.04514699906748361</v>
+        <v>2.035342464903226</v>
       </c>
       <c r="G38">
-        <v>-10.38752821591341</v>
+        <v>-10.16990829514886</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.572940753480068</v>
       </c>
       <c r="E39">
-        <v>-28.10438085515645</v>
+        <v>-26.9000035627034</v>
       </c>
       <c r="F39">
-        <v>-0.5517450246583548</v>
+        <v>2.158929911196495</v>
       </c>
       <c r="G39">
-        <v>-10.12152728175865</v>
+        <v>-10.26077134452567</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.718995493556741</v>
       </c>
       <c r="E40">
-        <v>-26.43117245551145</v>
+        <v>-27.67248010306488</v>
       </c>
       <c r="F40">
-        <v>0.3498483998138214</v>
+        <v>1.88041456629244</v>
       </c>
       <c r="G40">
-        <v>-10.64037099732895</v>
+        <v>-10.32305326749127</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.834433829276703</v>
       </c>
       <c r="E41">
-        <v>-28.86749398058612</v>
+        <v>-25.82208740188005</v>
       </c>
       <c r="F41">
-        <v>0.5356238721374582</v>
+        <v>2.060886002135951</v>
       </c>
       <c r="G41">
-        <v>-10.59526646840058</v>
+        <v>-10.13455359189601</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.91993744858271</v>
       </c>
       <c r="E42">
-        <v>-28.15163609361035</v>
+        <v>-26.09010658830521</v>
       </c>
       <c r="F42">
-        <v>0.2621300904291734</v>
+        <v>2.287298694138724</v>
       </c>
       <c r="G42">
-        <v>-9.593570762193057</v>
+        <v>-10.04016864806578</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.97519682282501</v>
       </c>
       <c r="E43">
-        <v>-27.78950098535325</v>
+        <v>-25.51841289623124</v>
       </c>
       <c r="F43">
-        <v>0.002952154176069686</v>
+        <v>2.315193138060594</v>
       </c>
       <c r="G43">
-        <v>-10.61684688319073</v>
+        <v>-10.43359872034049</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.00381106809114</v>
       </c>
       <c r="E44">
-        <v>-27.37482775383707</v>
+        <v>-24.82767155474238</v>
       </c>
       <c r="F44">
-        <v>0.2505669098534951</v>
+        <v>2.380612625329282</v>
       </c>
       <c r="G44">
-        <v>-10.59460595001903</v>
+        <v>-10.29596026549699</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.009787341113399</v>
       </c>
       <c r="E45">
-        <v>-28.01239137752283</v>
+        <v>-24.09192601533768</v>
       </c>
       <c r="F45">
-        <v>0.470241661401896</v>
+        <v>2.388831686699859</v>
       </c>
       <c r="G45">
-        <v>-10.98520597515697</v>
+        <v>-10.59650657208136</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.000931127313294</v>
       </c>
       <c r="E46">
-        <v>-26.79226926093735</v>
+        <v>-24.15735985976035</v>
       </c>
       <c r="F46">
-        <v>0.2236590515083588</v>
+        <v>2.180702720011678</v>
       </c>
       <c r="G46">
-        <v>-11.11452529236088</v>
+        <v>-10.60549014421938</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.985592141521686</v>
       </c>
       <c r="E47">
-        <v>-24.93574226662574</v>
+        <v>-23.88519576843301</v>
       </c>
       <c r="F47">
-        <v>0.5336473875143786</v>
+        <v>2.408551801090904</v>
       </c>
       <c r="G47">
-        <v>-11.20864394024281</v>
+        <v>-10.9237673226943</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.974379389299324</v>
       </c>
       <c r="E48">
-        <v>-24.511574794021</v>
+        <v>-23.13946590900342</v>
       </c>
       <c r="F48">
-        <v>-0.0736560916022314</v>
+        <v>2.690953845848895</v>
       </c>
       <c r="G48">
-        <v>-11.26350351633587</v>
+        <v>-10.69339130385758</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.977796570672302</v>
       </c>
       <c r="E49">
-        <v>-25.09262151799849</v>
+        <v>-23.36515556560593</v>
       </c>
       <c r="F49">
-        <v>-0.1134881381658456</v>
+        <v>2.614237083940827</v>
       </c>
       <c r="G49">
-        <v>-10.74808118155222</v>
+        <v>-10.94107786470568</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.005751841684861</v>
       </c>
       <c r="E50">
-        <v>-25.41839110789539</v>
+        <v>-22.76065565727714</v>
       </c>
       <c r="F50">
-        <v>0.4543850525775079</v>
+        <v>2.413053149557717</v>
       </c>
       <c r="G50">
-        <v>-11.01233422220323</v>
+        <v>-11.55832054391504</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.067784097756154</v>
       </c>
       <c r="E51">
-        <v>-25.04368422895804</v>
+        <v>-22.16841187556791</v>
       </c>
       <c r="F51">
-        <v>0.1345847046853279</v>
+        <v>2.193177933097838</v>
       </c>
       <c r="G51">
-        <v>-11.29941952967582</v>
+        <v>-11.44149363957961</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.169332438080826</v>
       </c>
       <c r="E52">
-        <v>-25.36140904851874</v>
+        <v>-22.78753939418275</v>
       </c>
       <c r="F52">
-        <v>-0.1239653290764538</v>
+        <v>2.37193630515236</v>
       </c>
       <c r="G52">
-        <v>-11.31124359192897</v>
+        <v>-11.18833887418543</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.316487304892667</v>
       </c>
       <c r="E53">
-        <v>-24.43043765757915</v>
+        <v>-20.67702691451258</v>
       </c>
       <c r="F53">
-        <v>0.5315491328830874</v>
+        <v>2.578900587272206</v>
       </c>
       <c r="G53">
-        <v>-11.4115014057169</v>
+        <v>-11.16990440662757</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.50793463619153</v>
       </c>
       <c r="E54">
-        <v>-22.13853782650842</v>
+        <v>-20.82763481678484</v>
       </c>
       <c r="F54">
-        <v>0.4911007809717903</v>
+        <v>2.189044379757869</v>
       </c>
       <c r="G54">
-        <v>-11.28784087741423</v>
+        <v>-11.34544042995567</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.746185105803935</v>
       </c>
       <c r="E55">
-        <v>-24.18608762249419</v>
+        <v>-20.79622823274649</v>
       </c>
       <c r="F55">
-        <v>0.4515271850378496</v>
+        <v>2.066296898011038</v>
       </c>
       <c r="G55">
-        <v>-11.3584732669545</v>
+        <v>-11.06198666820932</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.024541409798058</v>
       </c>
       <c r="E56">
-        <v>-23.34185189686232</v>
+        <v>-20.36617565969446</v>
       </c>
       <c r="F56">
-        <v>0.2237634258011115</v>
+        <v>2.294424310537605</v>
       </c>
       <c r="G56">
-        <v>-11.87701283077995</v>
+        <v>-11.8570210540735</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.342286841664913</v>
       </c>
       <c r="E57">
-        <v>-23.3362782872644</v>
+        <v>-19.22249339754245</v>
       </c>
       <c r="F57">
-        <v>0.4354527155865252</v>
+        <v>2.652492747336914</v>
       </c>
       <c r="G57">
-        <v>-12.15554925508894</v>
+        <v>-11.90072883464562</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.689150906076618</v>
       </c>
       <c r="E58">
-        <v>-22.24134641964323</v>
+        <v>-19.27066649569914</v>
       </c>
       <c r="F58">
-        <v>-0.2096856162855494</v>
+        <v>2.439897223612837</v>
       </c>
       <c r="G58">
-        <v>-11.92807246812065</v>
+        <v>-12.25843608868012</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.062054100619607</v>
       </c>
       <c r="E59">
-        <v>-21.84346877472465</v>
+        <v>-19.02676916064858</v>
       </c>
       <c r="F59">
-        <v>-0.1935291384613478</v>
+        <v>2.310317367527716</v>
       </c>
       <c r="G59">
-        <v>-12.11756944814972</v>
+        <v>-12.56510198058606</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.449314602102159</v>
       </c>
       <c r="E60">
-        <v>-22.11197804008614</v>
+        <v>-18.91957062314344</v>
       </c>
       <c r="F60">
-        <v>-0.1097422607703862</v>
+        <v>2.335271107169648</v>
       </c>
       <c r="G60">
-        <v>-11.99428878318505</v>
+        <v>-12.09744713421371</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.847687354146167</v>
       </c>
       <c r="E61">
-        <v>-20.49975954874625</v>
+        <v>-18.57987946888571</v>
       </c>
       <c r="F61">
-        <v>0.1190113975126972</v>
+        <v>2.080945747162144</v>
       </c>
       <c r="G61">
-        <v>-12.09416281751809</v>
+        <v>-12.37992969897217</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.247229938485696</v>
       </c>
       <c r="E62">
-        <v>-20.21811782917565</v>
+        <v>-18.04870865970809</v>
       </c>
       <c r="F62">
-        <v>0.227954964859277</v>
+        <v>2.19202153220353</v>
       </c>
       <c r="G62">
-        <v>-11.89024016825082</v>
+        <v>-12.9819073545573</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.646105689836276</v>
       </c>
       <c r="E63">
-        <v>-21.74414472589138</v>
+        <v>-18.36036148431189</v>
       </c>
       <c r="F63">
-        <v>-0.6882839952943945</v>
+        <v>2.312346867664575</v>
       </c>
       <c r="G63">
-        <v>-12.24778425074838</v>
+        <v>-13.11776528158965</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.036973970860763</v>
       </c>
       <c r="E64">
-        <v>-20.39761131621209</v>
+        <v>-17.1102614883838</v>
       </c>
       <c r="F64">
-        <v>-0.06322197579656882</v>
+        <v>2.298287816104262</v>
       </c>
       <c r="G64">
-        <v>-12.39196784228179</v>
+        <v>-12.7879238099484</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.418898943465709</v>
       </c>
       <c r="E65">
-        <v>-21.66946998627096</v>
+        <v>-18.08347934491955</v>
       </c>
       <c r="F65">
-        <v>0.4377439798226686</v>
+        <v>1.781688082491989</v>
       </c>
       <c r="G65">
-        <v>-12.54525510020442</v>
+        <v>-13.16294682748346</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.787541938894224</v>
       </c>
       <c r="E66">
-        <v>-19.71960372064516</v>
+        <v>-16.90162907069237</v>
       </c>
       <c r="F66">
-        <v>-0.1848047729750635</v>
+        <v>2.190035107171617</v>
       </c>
       <c r="G66">
-        <v>-13.5090963152131</v>
+        <v>-13.19797779840702</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.142259495918523</v>
       </c>
       <c r="E67">
-        <v>-19.4660377096304</v>
+        <v>-18.57823479720108</v>
       </c>
       <c r="F67">
-        <v>-0.1156940805595007</v>
+        <v>2.167110867666543</v>
       </c>
       <c r="G67">
-        <v>-12.29509355348394</v>
+        <v>-12.9505000971262</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.480026532245322</v>
       </c>
       <c r="E68">
-        <v>-20.12589161849651</v>
+        <v>-17.67194178795361</v>
       </c>
       <c r="F68">
-        <v>0.04290348564568704</v>
+        <v>2.007013956462289</v>
       </c>
       <c r="G68">
-        <v>-12.25767636200411</v>
+        <v>-13.09509879704961</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.798504009561023</v>
       </c>
       <c r="E69">
-        <v>-18.91214468129464</v>
+        <v>-18.41937861723771</v>
       </c>
       <c r="F69">
-        <v>-0.2236179276332343</v>
+        <v>1.857607954958564</v>
       </c>
       <c r="G69">
-        <v>-12.35948365270687</v>
+        <v>-12.84460438039376</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.095450082002037</v>
       </c>
       <c r="E70">
-        <v>-21.35998098476739</v>
+        <v>-17.8661459495026</v>
       </c>
       <c r="F70">
-        <v>-0.4774843720995876</v>
+        <v>1.851746427216355</v>
       </c>
       <c r="G70">
-        <v>-12.57813220684031</v>
+        <v>-12.82304093544346</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.367271303548652</v>
       </c>
       <c r="E71">
-        <v>-19.87153649733003</v>
+        <v>-17.47668271072813</v>
       </c>
       <c r="F71">
-        <v>-0.311635277650293</v>
+        <v>1.912089679040687</v>
       </c>
       <c r="G71">
-        <v>-12.85741008261317</v>
+        <v>-12.74031557695715</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.61342799313379</v>
       </c>
       <c r="E72">
-        <v>-20.74707912992846</v>
+        <v>-18.37297063389407</v>
       </c>
       <c r="F72">
-        <v>-0.6331138979005447</v>
+        <v>2.035919008615574</v>
       </c>
       <c r="G72">
-        <v>-12.24391382189205</v>
+        <v>-13.28208685152662</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.829797923140383</v>
       </c>
       <c r="E73">
-        <v>-19.57144205984322</v>
+        <v>-17.62295466037726</v>
       </c>
       <c r="F73">
-        <v>-0.9171478264420504</v>
+        <v>1.729681520209431</v>
       </c>
       <c r="G73">
-        <v>-12.32749680997655</v>
+        <v>-12.86995340500118</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.0163298051425</v>
       </c>
       <c r="E74">
-        <v>-20.53016105564399</v>
+        <v>-18.45153693252585</v>
       </c>
       <c r="F74">
-        <v>-0.7714611945768958</v>
+        <v>1.783949525501632</v>
       </c>
       <c r="G74">
-        <v>-13.49175966575581</v>
+        <v>-13.13063364167925</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.1676967629804</v>
       </c>
       <c r="E75">
-        <v>-20.23235503759716</v>
+        <v>-18.11387254539465</v>
       </c>
       <c r="F75">
-        <v>-0.6281089020528301</v>
+        <v>1.825044832354515</v>
       </c>
       <c r="G75">
-        <v>-11.36949583061819</v>
+        <v>-12.3104708391256</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.28298156872317</v>
       </c>
       <c r="E76">
-        <v>-22.93302638689149</v>
+        <v>-19.59484955886996</v>
       </c>
       <c r="F76">
-        <v>-0.05347126309821584</v>
+        <v>2.080773446742362</v>
       </c>
       <c r="G76">
-        <v>-11.38400895980018</v>
+        <v>-12.11500830770584</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.35556592439862</v>
       </c>
       <c r="E77">
-        <v>-20.7412314083831</v>
+        <v>-20.00502070931002</v>
       </c>
       <c r="F77">
-        <v>-0.3062848525956109</v>
+        <v>1.456028691959808</v>
       </c>
       <c r="G77">
-        <v>-11.17384924170475</v>
+        <v>-12.50526632530234</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.38318825547877</v>
       </c>
       <c r="E78">
-        <v>-21.76397215675611</v>
+        <v>-19.33755811729683</v>
       </c>
       <c r="F78">
-        <v>-0.9581636100242651</v>
+        <v>1.829489851837938</v>
       </c>
       <c r="G78">
-        <v>-12.23615338359497</v>
+        <v>-12.42073302618668</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.35818616516516</v>
       </c>
       <c r="E79">
-        <v>-22.63191025941878</v>
+        <v>-20.36974326822249</v>
       </c>
       <c r="F79">
-        <v>-1.227754952897961</v>
+        <v>1.564496776417181</v>
       </c>
       <c r="G79">
-        <v>-11.38000668834201</v>
+        <v>-11.73279921568374</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.27779556207686</v>
       </c>
       <c r="E80">
-        <v>-23.25408623514604</v>
+        <v>-19.8784557473972</v>
       </c>
       <c r="F80">
-        <v>-0.2374574618318056</v>
+        <v>1.649735782165251</v>
       </c>
       <c r="G80">
-        <v>-11.38016333301747</v>
+        <v>-11.64432891372468</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.13470299046288</v>
       </c>
       <c r="E81">
-        <v>-22.12504819612538</v>
+        <v>-20.98046053390456</v>
       </c>
       <c r="F81">
-        <v>-0.9731901947110482</v>
+        <v>1.580795733434665</v>
       </c>
       <c r="G81">
-        <v>-10.68102681747406</v>
+        <v>-11.54957193879022</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.927639393001394</v>
       </c>
       <c r="E82">
-        <v>-23.4162525245353</v>
+        <v>-21.99798069564225</v>
       </c>
       <c r="F82">
-        <v>-0.7717130182673467</v>
+        <v>1.489007655000062</v>
       </c>
       <c r="G82">
-        <v>-11.36885097670418</v>
+        <v>-11.1828523944272</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.650939047322529</v>
       </c>
       <c r="E83">
-        <v>-24.07125548257401</v>
+        <v>-22.21211196512776</v>
       </c>
       <c r="F83">
-        <v>-0.6730494903895089</v>
+        <v>1.636115765328421</v>
       </c>
       <c r="G83">
-        <v>-11.37835147627124</v>
+        <v>-10.89547076744352</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.307286709995166</v>
       </c>
       <c r="E84">
-        <v>-25.22618048778233</v>
+        <v>-23.19330398740718</v>
       </c>
       <c r="F84">
-        <v>-1.067050848387455</v>
+        <v>1.798626539144434</v>
       </c>
       <c r="G84">
-        <v>-11.3435215326812</v>
+        <v>-11.37005191921609</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.895072564074876</v>
       </c>
       <c r="E85">
-        <v>-25.54965750502792</v>
+        <v>-23.0432609218751</v>
       </c>
       <c r="F85">
-        <v>-0.5821469367084995</v>
+        <v>1.667713011540805</v>
       </c>
       <c r="G85">
-        <v>-10.92549955173051</v>
+        <v>-11.21064246522731</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.423871003280063</v>
       </c>
       <c r="E86">
-        <v>-26.98111162666598</v>
+        <v>-25.29557234259756</v>
       </c>
       <c r="F86">
-        <v>-0.8213198001839952</v>
+        <v>1.516103552745634</v>
       </c>
       <c r="G86">
-        <v>-9.363723419136035</v>
+        <v>-11.04476358614174</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.898311263200092</v>
       </c>
       <c r="E87">
-        <v>-26.75935090797676</v>
+        <v>-25.89784612965625</v>
       </c>
       <c r="F87">
-        <v>-1.24491955385137</v>
+        <v>1.554639204323867</v>
       </c>
       <c r="G87">
-        <v>-10.7372178733086</v>
+        <v>-10.96997097509553</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.335905043526104</v>
       </c>
       <c r="E88">
-        <v>-27.78435930973312</v>
+        <v>-26.32080917097679</v>
       </c>
       <c r="F88">
-        <v>-0.7186941910185672</v>
+        <v>1.484325722439439</v>
       </c>
       <c r="G88">
-        <v>-9.816459165542467</v>
+        <v>-10.29711551997856</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.746385001412209</v>
       </c>
       <c r="E89">
-        <v>-29.36672867128146</v>
+        <v>-28.49761936302519</v>
       </c>
       <c r="F89">
-        <v>-0.7086378107485812</v>
+        <v>1.54969550766396</v>
       </c>
       <c r="G89">
-        <v>-9.824472846064889</v>
+        <v>-10.09630096214701</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.152430058130394</v>
       </c>
       <c r="E90">
-        <v>-30.67686333690995</v>
+        <v>-29.01377631326356</v>
       </c>
       <c r="F90">
-        <v>-1.626408422230029</v>
+        <v>1.304666086650672</v>
       </c>
       <c r="G90">
-        <v>-10.59654964936712</v>
+        <v>-10.08756541074515</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.564628576819625</v>
       </c>
       <c r="E91">
-        <v>-31.344886612452</v>
+        <v>-30.73358166736747</v>
       </c>
       <c r="F91">
-        <v>-1.304891697079249</v>
+        <v>1.600853821726052</v>
       </c>
       <c r="G91">
-        <v>-10.95908678089518</v>
+        <v>-9.711067322516111</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.00515970704727</v>
       </c>
       <c r="E92">
-        <v>-33.39794979647148</v>
+        <v>-32.26881208037902</v>
       </c>
       <c r="F92">
-        <v>-1.588011108008064</v>
+        <v>1.391054866353826</v>
       </c>
       <c r="G92">
-        <v>-10.35088119408795</v>
+        <v>-9.671789975515107</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.479359390573422</v>
       </c>
       <c r="E93">
-        <v>-34.57397311520993</v>
+        <v>-33.17161016229664</v>
       </c>
       <c r="F93">
-        <v>-1.073802042720271</v>
+        <v>1.191297380638337</v>
       </c>
       <c r="G93">
-        <v>-10.23559071294438</v>
+        <v>-9.36875432396311</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.001910103764659</v>
       </c>
       <c r="E94">
-        <v>-34.86636542229485</v>
+        <v>-35.12298404363335</v>
       </c>
       <c r="F94">
-        <v>-0.9945877530927622</v>
+        <v>1.149048986360756</v>
       </c>
       <c r="G94">
-        <v>-10.65300047428846</v>
+        <v>-8.996013097200684</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.568613323021618</v>
       </c>
       <c r="E95">
-        <v>-38.88727204715965</v>
+        <v>-36.92997568647373</v>
       </c>
       <c r="F95">
-        <v>-0.9719418450350292</v>
+        <v>1.12380697486265</v>
       </c>
       <c r="G95">
-        <v>-10.77374088476598</v>
+        <v>-9.227296349782819</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.178768817225829</v>
       </c>
       <c r="E96">
-        <v>-39.75935090151317</v>
+        <v>-38.81031511791624</v>
       </c>
       <c r="F96">
-        <v>-1.81777454615516</v>
+        <v>1.028779979883102</v>
       </c>
       <c r="G96">
-        <v>-10.61618114331999</v>
+        <v>-8.848891112629973</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.819008840983257</v>
       </c>
       <c r="E97">
-        <v>-40.3579428667324</v>
+        <v>-39.96673320259584</v>
       </c>
       <c r="F97">
-        <v>-1.591877927044332</v>
+        <v>0.8176920848321206</v>
       </c>
       <c r="G97">
-        <v>-10.55290191592059</v>
+        <v>-9.030507560110768</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.474427090449209</v>
       </c>
       <c r="E98">
-        <v>-42.55423784971124</v>
+        <v>-42.1828286205658</v>
       </c>
       <c r="F98">
-        <v>-1.900148229056945</v>
+        <v>0.75044024886844</v>
       </c>
       <c r="G98">
-        <v>-10.32105213176218</v>
+        <v>-8.793680391389405</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.133503153114299</v>
       </c>
       <c r="E99">
-        <v>-44.75977372788783</v>
+        <v>-43.45944894740858</v>
       </c>
       <c r="F99">
-        <v>-2.33770265999188</v>
+        <v>0.2562271443168241</v>
       </c>
       <c r="G99">
-        <v>-10.81762227985341</v>
+        <v>-8.910837554915613</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.776300867046665</v>
       </c>
       <c r="E100">
-        <v>-46.97822401667896</v>
+        <v>-45.94711766239493</v>
       </c>
       <c r="F100">
-        <v>-2.263577859687172</v>
+        <v>0.1466796971336035</v>
       </c>
       <c r="G100">
-        <v>-11.43787775832092</v>
+        <v>-9.689826304522812</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.410089842087177</v>
       </c>
       <c r="E101">
-        <v>-49.87238206026592</v>
+        <v>-47.08648577628328</v>
       </c>
       <c r="F101">
-        <v>-2.568232337986566</v>
+        <v>-0.2370159420061135</v>
       </c>
       <c r="G101">
-        <v>-11.39613325768132</v>
+        <v>-9.352178706554131</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.011535182307246</v>
       </c>
       <c r="E102">
-        <v>-50.13014385302159</v>
+        <v>-49.57558942578235</v>
       </c>
       <c r="F102">
-        <v>-2.45501687994375</v>
+        <v>-0.4833914600489508</v>
       </c>
       <c r="G102">
-        <v>-10.75706736443483</v>
+        <v>-8.897738143929702</v>
       </c>
     </row>
   </sheetData>
